--- a/docs/SCIT 2026 Lab Bookings.xlsx
+++ b/docs/SCIT 2026 Lab Bookings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\EIS SCIT\Teaching and Learning\Timetabling\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/taliaveils/Documents/my-coding-project/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4FE8A0BD-BBBD-4E16-873B-4FD1270FAA9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D08C5B34-DB30-5D48-B170-77658C7B37C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3324" uniqueCount="540">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3601" uniqueCount="541">
   <si>
     <t>Activity Type Name</t>
   </si>
@@ -1640,13 +1640,16 @@
   </si>
   <si>
     <t>22/07/2026</t>
+  </si>
+  <si>
+    <t>Capicity</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1666,6 +1669,12 @@
       <sz val="8.25"/>
       <color rgb="FF000000"/>
       <name val="Tahoma"/>
+    </font>
+    <font>
+      <sz val="8.25"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1748,7 +1757,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1758,6 +1767,15 @@
     </xf>
     <xf numFmtId="49" fontId="3" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2093,15 +2111,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L277"/>
-  <sheetFormatPr defaultColWidth="16" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M277"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="16" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="51.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="51.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="55.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="103.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="103.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2129,17 +2147,20 @@
       <c r="I1" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -2167,17 +2188,20 @@
       <c r="I2" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -2205,17 +2229,20 @@
       <c r="I3" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="M3" s="2" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
@@ -2243,17 +2270,20 @@
       <c r="I4" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K4" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="M4" s="2" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
@@ -2281,17 +2311,20 @@
       <c r="I5" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="J5" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="L5" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="M5" s="2" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
@@ -2319,17 +2352,20 @@
       <c r="I6" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="J6" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K6" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="L6" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="L6" s="2" t="s">
+      <c r="M6" s="2" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>1</v>
       </c>
@@ -2357,17 +2393,20 @@
       <c r="I7" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="J7" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K7" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="L7" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="M7" s="2" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>1</v>
       </c>
@@ -2395,17 +2434,20 @@
       <c r="I8" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="J8" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K8" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="L8" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="L8" s="2" t="s">
+      <c r="M8" s="2" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>1</v>
       </c>
@@ -2433,17 +2475,20 @@
       <c r="I9" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="J9" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K9" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K9" s="2" t="s">
+      <c r="L9" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="L9" s="2" t="s">
+      <c r="M9" s="2" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>1</v>
       </c>
@@ -2471,17 +2516,20 @@
       <c r="I10" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="J10" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K10" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="L10" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="L10" s="2" t="s">
+      <c r="M10" s="2" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>1</v>
       </c>
@@ -2509,17 +2557,20 @@
       <c r="I11" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J11" s="3" t="s">
+      <c r="J11" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K11" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="L11" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="L11" s="2" t="s">
+      <c r="M11" s="2" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>1</v>
       </c>
@@ -2547,17 +2598,20 @@
       <c r="I12" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="J12" s="3" t="s">
+      <c r="J12" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="K12" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="K12" s="2" t="s">
+      <c r="L12" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="L12" s="2" t="s">
+      <c r="M12" s="2" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>1</v>
       </c>
@@ -2585,17 +2639,20 @@
       <c r="I13" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="J13" s="3" t="s">
+      <c r="J13" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="K13" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="K13" s="2" t="s">
+      <c r="L13" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="L13" s="2" t="s">
+      <c r="M13" s="2" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>1</v>
       </c>
@@ -2623,17 +2680,20 @@
       <c r="I14" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="J14" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="K14" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="K14" s="2" t="s">
+      <c r="L14" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="L14" s="2" t="s">
+      <c r="M14" s="2" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>1</v>
       </c>
@@ -2661,17 +2721,20 @@
       <c r="I15" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="J15" s="3" t="s">
+      <c r="J15" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="K15" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="K15" s="2" t="s">
+      <c r="L15" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="L15" s="2" t="s">
+      <c r="M15" s="2" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>1</v>
       </c>
@@ -2699,17 +2762,20 @@
       <c r="I16" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="J16" s="3" t="s">
+      <c r="J16" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="K16" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="K16" s="2" t="s">
+      <c r="L16" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="L16" s="2" t="s">
+      <c r="M16" s="2" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>1</v>
       </c>
@@ -2737,17 +2803,20 @@
       <c r="I17" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J17" s="3" t="s">
+      <c r="J17" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K17" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K17" s="2" t="s">
+      <c r="L17" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="L17" s="2" t="s">
+      <c r="M17" s="2" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>1</v>
       </c>
@@ -2775,17 +2844,20 @@
       <c r="I18" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J18" s="3" t="s">
+      <c r="J18" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K18" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K18" s="2" t="s">
+      <c r="L18" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="L18" s="2" t="s">
+      <c r="M18" s="2" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>1</v>
       </c>
@@ -2813,17 +2885,20 @@
       <c r="I19" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J19" s="3" t="s">
+      <c r="J19" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K19" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K19" s="2" t="s">
+      <c r="L19" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="L19" s="2" t="s">
+      <c r="M19" s="2" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>1</v>
       </c>
@@ -2851,17 +2926,20 @@
       <c r="I20" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J20" s="3" t="s">
+      <c r="J20" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K20" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K20" s="2" t="s">
+      <c r="L20" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="L20" s="2" t="s">
+      <c r="M20" s="2" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>1</v>
       </c>
@@ -2889,17 +2967,20 @@
       <c r="I21" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="J21" s="3" t="s">
+      <c r="J21" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="K21" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K21" s="2" t="s">
+      <c r="L21" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="L21" s="2" t="s">
+      <c r="M21" s="2" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>1</v>
       </c>
@@ -2927,17 +3008,20 @@
       <c r="I22" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J22" s="3" t="s">
+      <c r="J22" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K22" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K22" s="2" t="s">
+      <c r="L22" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="L22" s="2" t="s">
+      <c r="M22" s="2" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>1</v>
       </c>
@@ -2965,17 +3049,20 @@
       <c r="I23" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="J23" s="3" t="s">
+      <c r="J23" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K23" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K23" s="2" t="s">
+      <c r="L23" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="L23" s="2" t="s">
+      <c r="M23" s="2" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>1</v>
       </c>
@@ -3003,17 +3090,20 @@
       <c r="I24" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="J24" s="3" t="s">
+      <c r="J24" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K24" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K24" s="2" t="s">
+      <c r="L24" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="L24" s="2" t="s">
+      <c r="M24" s="2" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>2</v>
       </c>
@@ -3041,17 +3131,20 @@
       <c r="I25" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="J25" s="3" t="s">
+      <c r="J25" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K25" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K25" s="2" t="s">
+      <c r="L25" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="L25" s="2" t="s">
+      <c r="M25" s="2" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>2</v>
       </c>
@@ -3079,17 +3172,20 @@
       <c r="I26" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="J26" s="3" t="s">
+      <c r="J26" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K26" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K26" s="2" t="s">
+      <c r="L26" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="L26" s="2" t="s">
+      <c r="M26" s="2" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>2</v>
       </c>
@@ -3117,17 +3213,20 @@
       <c r="I27" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="J27" s="3" t="s">
+      <c r="J27" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K27" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K27" s="2" t="s">
+      <c r="L27" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="L27" s="2" t="s">
+      <c r="M27" s="2" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>2</v>
       </c>
@@ -3155,17 +3254,20 @@
       <c r="I28" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="J28" s="3" t="s">
+      <c r="J28" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K28" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K28" s="2" t="s">
+      <c r="L28" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="L28" s="2" t="s">
+      <c r="M28" s="2" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>2</v>
       </c>
@@ -3193,17 +3295,20 @@
       <c r="I29" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="J29" s="3" t="s">
+      <c r="J29" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K29" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K29" s="2" t="s">
+      <c r="L29" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="L29" s="2" t="s">
+      <c r="M29" s="2" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>1</v>
       </c>
@@ -3231,17 +3336,20 @@
       <c r="I30" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J30" s="3" t="s">
+      <c r="J30" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K30" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K30" s="2" t="s">
+      <c r="L30" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="L30" s="2" t="s">
+      <c r="M30" s="2" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>1</v>
       </c>
@@ -3269,17 +3377,20 @@
       <c r="I31" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J31" s="3" t="s">
+      <c r="J31" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K31" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K31" s="2" t="s">
+      <c r="L31" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="L31" s="2" t="s">
+      <c r="M31" s="2" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>1</v>
       </c>
@@ -3307,17 +3418,20 @@
       <c r="I32" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J32" s="3" t="s">
+      <c r="J32" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K32" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K32" s="2" t="s">
+      <c r="L32" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="L32" s="2" t="s">
+      <c r="M32" s="2" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>1</v>
       </c>
@@ -3345,17 +3459,20 @@
       <c r="I33" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J33" s="3" t="s">
+      <c r="J33" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K33" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K33" s="2" t="s">
+      <c r="L33" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="L33" s="2" t="s">
+      <c r="M33" s="2" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>1</v>
       </c>
@@ -3383,17 +3500,20 @@
       <c r="I34" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J34" s="3" t="s">
+      <c r="J34" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K34" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K34" s="2" t="s">
+      <c r="L34" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="L34" s="2" t="s">
+      <c r="M34" s="2" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>1</v>
       </c>
@@ -3421,17 +3541,20 @@
       <c r="I35" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J35" s="3" t="s">
+      <c r="J35" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K35" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K35" s="2" t="s">
+      <c r="L35" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="L35" s="2" t="s">
+      <c r="M35" s="2" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>1</v>
       </c>
@@ -3459,17 +3582,20 @@
       <c r="I36" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J36" s="3" t="s">
+      <c r="J36" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K36" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K36" s="2" t="s">
+      <c r="L36" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="L36" s="2" t="s">
+      <c r="M36" s="2" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>1</v>
       </c>
@@ -3497,17 +3623,20 @@
       <c r="I37" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J37" s="3" t="s">
+      <c r="J37" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K37" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K37" s="2" t="s">
+      <c r="L37" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="L37" s="2" t="s">
+      <c r="M37" s="2" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>1</v>
       </c>
@@ -3535,17 +3664,20 @@
       <c r="I38" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J38" s="3" t="s">
+      <c r="J38" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K38" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K38" s="2" t="s">
+      <c r="L38" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="L38" s="2" t="s">
+      <c r="M38" s="2" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>1</v>
       </c>
@@ -3573,17 +3705,20 @@
       <c r="I39" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J39" s="3" t="s">
+      <c r="J39" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K39" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K39" s="2" t="s">
+      <c r="L39" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="L39" s="2" t="s">
+      <c r="M39" s="2" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>1</v>
       </c>
@@ -3611,17 +3746,20 @@
       <c r="I40" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J40" s="3" t="s">
+      <c r="J40" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K40" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K40" s="2" t="s">
+      <c r="L40" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="L40" s="2" t="s">
+      <c r="M40" s="2" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>1</v>
       </c>
@@ -3649,17 +3787,20 @@
       <c r="I41" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J41" s="3" t="s">
+      <c r="J41" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K41" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K41" s="2" t="s">
+      <c r="L41" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="L41" s="2" t="s">
+      <c r="M41" s="2" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>1</v>
       </c>
@@ -3687,17 +3828,20 @@
       <c r="I42" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J42" s="3" t="s">
+      <c r="J42" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K42" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K42" s="2" t="s">
+      <c r="L42" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="L42" s="2" t="s">
+      <c r="M42" s="2" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>1</v>
       </c>
@@ -3725,17 +3869,20 @@
       <c r="I43" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J43" s="3" t="s">
+      <c r="J43" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K43" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K43" s="2" t="s">
+      <c r="L43" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="L43" s="2" t="s">
+      <c r="M43" s="2" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>1</v>
       </c>
@@ -3763,17 +3910,20 @@
       <c r="I44" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J44" s="3" t="s">
+      <c r="J44" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K44" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K44" s="2" t="s">
+      <c r="L44" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="L44" s="2" t="s">
+      <c r="M44" s="2" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>1</v>
       </c>
@@ -3801,17 +3951,20 @@
       <c r="I45" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J45" s="3" t="s">
+      <c r="J45" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K45" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K45" s="2" t="s">
+      <c r="L45" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="L45" s="2" t="s">
+      <c r="M45" s="2" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>1</v>
       </c>
@@ -3839,17 +3992,20 @@
       <c r="I46" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J46" s="3" t="s">
+      <c r="J46" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K46" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K46" s="2" t="s">
+      <c r="L46" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="L46" s="2" t="s">
+      <c r="M46" s="2" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>1</v>
       </c>
@@ -3877,17 +4033,20 @@
       <c r="I47" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J47" s="3" t="s">
+      <c r="J47" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K47" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K47" s="2" t="s">
+      <c r="L47" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="L47" s="2" t="s">
+      <c r="M47" s="2" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>1</v>
       </c>
@@ -3915,17 +4074,20 @@
       <c r="I48" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J48" s="3" t="s">
+      <c r="J48" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K48" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K48" s="2" t="s">
+      <c r="L48" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="L48" s="2" t="s">
+      <c r="M48" s="2" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
         <v>1</v>
       </c>
@@ -3953,17 +4115,20 @@
       <c r="I49" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J49" s="3" t="s">
+      <c r="J49" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K49" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K49" s="2" t="s">
+      <c r="L49" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="L49" s="2" t="s">
+      <c r="M49" s="2" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>1</v>
       </c>
@@ -3991,17 +4156,20 @@
       <c r="I50" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="J50" s="3" t="s">
+      <c r="J50" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K50" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K50" s="2" t="s">
+      <c r="L50" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="L50" s="2" t="s">
+      <c r="M50" s="2" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="51" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
         <v>1</v>
       </c>
@@ -4029,17 +4197,20 @@
       <c r="I51" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="J51" s="3" t="s">
+      <c r="J51" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K51" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K51" s="2" t="s">
+      <c r="L51" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="L51" s="2" t="s">
+      <c r="M51" s="2" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
         <v>1</v>
       </c>
@@ -4067,17 +4238,20 @@
       <c r="I52" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="J52" s="3" t="s">
+      <c r="J52" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K52" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K52" s="2" t="s">
+      <c r="L52" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="L52" s="2" t="s">
+      <c r="M52" s="2" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="53" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
         <v>2</v>
       </c>
@@ -4105,17 +4279,20 @@
       <c r="I53" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="J53" s="3" t="s">
+      <c r="J53" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K53" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K53" s="2" t="s">
+      <c r="L53" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="L53" s="2" t="s">
+      <c r="M53" s="2" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
         <v>2</v>
       </c>
@@ -4143,17 +4320,20 @@
       <c r="I54" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="J54" s="3" t="s">
+      <c r="J54" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K54" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K54" s="2" t="s">
+      <c r="L54" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="L54" s="2" t="s">
+      <c r="M54" s="2" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="55" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
         <v>2</v>
       </c>
@@ -4181,17 +4361,20 @@
       <c r="I55" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="J55" s="3" t="s">
+      <c r="J55" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K55" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K55" s="2" t="s">
+      <c r="L55" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="L55" s="2" t="s">
+      <c r="M55" s="2" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
         <v>2</v>
       </c>
@@ -4219,17 +4402,20 @@
       <c r="I56" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="J56" s="3" t="s">
+      <c r="J56" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K56" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K56" s="2" t="s">
+      <c r="L56" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="L56" s="2" t="s">
+      <c r="M56" s="2" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
         <v>2</v>
       </c>
@@ -4257,17 +4443,20 @@
       <c r="I57" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="J57" s="3" t="s">
+      <c r="J57" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K57" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K57" s="2" t="s">
+      <c r="L57" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="L57" s="2" t="s">
+      <c r="M57" s="2" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
         <v>2</v>
       </c>
@@ -4295,17 +4484,20 @@
       <c r="I58" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="J58" s="3" t="s">
+      <c r="J58" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K58" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K58" s="2" t="s">
+      <c r="L58" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="L58" s="2" t="s">
+      <c r="M58" s="2" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
         <v>2</v>
       </c>
@@ -4333,17 +4525,20 @@
       <c r="I59" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="J59" s="3" t="s">
+      <c r="J59" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K59" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K59" s="2" t="s">
+      <c r="L59" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="L59" s="2" t="s">
+      <c r="M59" s="2" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
         <v>2</v>
       </c>
@@ -4371,17 +4566,20 @@
       <c r="I60" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="J60" s="3" t="s">
+      <c r="J60" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K60" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K60" s="2" t="s">
+      <c r="L60" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="L60" s="2" t="s">
+      <c r="M60" s="2" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
         <v>2</v>
       </c>
@@ -4409,17 +4607,20 @@
       <c r="I61" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="J61" s="3" t="s">
+      <c r="J61" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K61" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K61" s="2" t="s">
+      <c r="L61" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="L61" s="2" t="s">
+      <c r="M61" s="2" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
         <v>1</v>
       </c>
@@ -4447,17 +4648,20 @@
       <c r="I62" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J62" s="3" t="s">
+      <c r="J62" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K62" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K62" s="2" t="s">
+      <c r="L62" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="L62" s="2" t="s">
+      <c r="M62" s="2" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
         <v>1</v>
       </c>
@@ -4485,17 +4689,20 @@
       <c r="I63" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="J63" s="3" t="s">
+      <c r="J63" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K63" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="K63" s="2" t="s">
+      <c r="L63" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="L63" s="2" t="s">
+      <c r="M63" s="2" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
         <v>1</v>
       </c>
@@ -4523,17 +4730,20 @@
       <c r="I64" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="J64" s="3" t="s">
+      <c r="J64" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K64" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="K64" s="2" t="s">
+      <c r="L64" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="L64" s="2" t="s">
+      <c r="M64" s="2" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
         <v>1</v>
       </c>
@@ -4561,17 +4771,20 @@
       <c r="I65" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="J65" s="3" t="s">
+      <c r="J65" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K65" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="K65" s="2" t="s">
+      <c r="L65" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="L65" s="2" t="s">
+      <c r="M65" s="2" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
         <v>1</v>
       </c>
@@ -4599,17 +4812,20 @@
       <c r="I66" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="J66" s="3" t="s">
+      <c r="J66" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K66" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="K66" s="2" t="s">
+      <c r="L66" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="L66" s="2" t="s">
+      <c r="M66" s="2" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
         <v>1</v>
       </c>
@@ -4637,17 +4853,20 @@
       <c r="I67" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="J67" s="3" t="s">
+      <c r="J67" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K67" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="K67" s="2" t="s">
+      <c r="L67" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="L67" s="2" t="s">
+      <c r="M67" s="2" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
         <v>1</v>
       </c>
@@ -4675,17 +4894,20 @@
       <c r="I68" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="J68" s="3" t="s">
+      <c r="J68" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K68" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="K68" s="2" t="s">
+      <c r="L68" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="L68" s="2" t="s">
+      <c r="M68" s="2" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
         <v>1</v>
       </c>
@@ -4713,17 +4935,20 @@
       <c r="I69" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="J69" s="3" t="s">
+      <c r="J69" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K69" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="K69" s="2" t="s">
+      <c r="L69" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="L69" s="2" t="s">
+      <c r="M69" s="2" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="70" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
         <v>1</v>
       </c>
@@ -4751,17 +4976,20 @@
       <c r="I70" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="J70" s="3" t="s">
+      <c r="J70" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K70" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="K70" s="2" t="s">
+      <c r="L70" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="L70" s="2" t="s">
+      <c r="M70" s="2" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="71" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
         <v>1</v>
       </c>
@@ -4789,17 +5017,20 @@
       <c r="I71" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="J71" s="3" t="s">
+      <c r="J71" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K71" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="K71" s="2" t="s">
+      <c r="L71" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="L71" s="2" t="s">
+      <c r="M71" s="2" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="72" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
         <v>1</v>
       </c>
@@ -4827,17 +5058,20 @@
       <c r="I72" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="J72" s="3" t="s">
+      <c r="J72" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K72" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="K72" s="2" t="s">
+      <c r="L72" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="L72" s="2" t="s">
+      <c r="M72" s="2" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="73" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
         <v>1</v>
       </c>
@@ -4865,17 +5099,20 @@
       <c r="I73" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="J73" s="3" t="s">
+      <c r="J73" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="K73" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="K73" s="2" t="s">
+      <c r="L73" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="L73" s="2" t="s">
+      <c r="M73" s="2" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
         <v>1</v>
       </c>
@@ -4903,17 +5140,20 @@
       <c r="I74" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="J74" s="3" t="s">
+      <c r="J74" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K74" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="K74" s="2" t="s">
+      <c r="L74" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="L74" s="2" t="s">
+      <c r="M74" s="2" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="75" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
         <v>1</v>
       </c>
@@ -4941,17 +5181,20 @@
       <c r="I75" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J75" s="3" t="s">
+      <c r="J75" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K75" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="K75" s="2" t="s">
+      <c r="L75" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="L75" s="2" t="s">
+      <c r="M75" s="2" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
         <v>1</v>
       </c>
@@ -4979,17 +5222,20 @@
       <c r="I76" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J76" s="3" t="s">
+      <c r="J76" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K76" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="K76" s="2" t="s">
+      <c r="L76" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="L76" s="2" t="s">
+      <c r="M76" s="2" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="77" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
         <v>1</v>
       </c>
@@ -5017,17 +5263,20 @@
       <c r="I77" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J77" s="3" t="s">
+      <c r="J77" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K77" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="K77" s="2" t="s">
+      <c r="L77" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="L77" s="2" t="s">
+      <c r="M77" s="2" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
         <v>1</v>
       </c>
@@ -5055,17 +5304,20 @@
       <c r="I78" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J78" s="3" t="s">
+      <c r="J78" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K78" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="K78" s="2" t="s">
+      <c r="L78" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="L78" s="2" t="s">
+      <c r="M78" s="2" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
         <v>1</v>
       </c>
@@ -5093,17 +5345,20 @@
       <c r="I79" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J79" s="3" t="s">
+      <c r="J79" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K79" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K79" s="2" t="s">
+      <c r="L79" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="L79" s="2" t="s">
+      <c r="M79" s="2" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
         <v>1</v>
       </c>
@@ -5131,17 +5386,20 @@
       <c r="I80" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J80" s="3" t="s">
+      <c r="J80" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K80" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="K80" s="2" t="s">
+      <c r="L80" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="L80" s="2" t="s">
+      <c r="M80" s="2" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
         <v>1</v>
       </c>
@@ -5169,17 +5427,20 @@
       <c r="I81" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J81" s="3" t="s">
+      <c r="J81" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K81" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="K81" s="2" t="s">
+      <c r="L81" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="L81" s="2" t="s">
+      <c r="M81" s="2" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="82" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
         <v>1</v>
       </c>
@@ -5207,17 +5468,20 @@
       <c r="I82" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J82" s="3" t="s">
+      <c r="J82" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K82" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="K82" s="2" t="s">
+      <c r="L82" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="L82" s="2" t="s">
+      <c r="M82" s="2" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="83" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="2" t="s">
         <v>1</v>
       </c>
@@ -5245,17 +5509,20 @@
       <c r="I83" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J83" s="3" t="s">
+      <c r="J83" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K83" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="K83" s="2" t="s">
+      <c r="L83" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="L83" s="2" t="s">
+      <c r="M83" s="2" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="84" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
         <v>1</v>
       </c>
@@ -5283,17 +5550,20 @@
       <c r="I84" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J84" s="3" t="s">
+      <c r="J84" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K84" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="K84" s="2" t="s">
+      <c r="L84" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="L84" s="2" t="s">
+      <c r="M84" s="2" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="85" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
         <v>1</v>
       </c>
@@ -5321,17 +5591,20 @@
       <c r="I85" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J85" s="3" t="s">
+      <c r="J85" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K85" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="K85" s="2" t="s">
+      <c r="L85" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="L85" s="2" t="s">
+      <c r="M85" s="2" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="86" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
         <v>1</v>
       </c>
@@ -5359,17 +5632,20 @@
       <c r="I86" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J86" s="3" t="s">
+      <c r="J86" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K86" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="K86" s="2" t="s">
+      <c r="L86" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="L86" s="2" t="s">
+      <c r="M86" s="2" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="87" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
         <v>1</v>
       </c>
@@ -5397,17 +5673,20 @@
       <c r="I87" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J87" s="3" t="s">
+      <c r="J87" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K87" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="K87" s="2" t="s">
+      <c r="L87" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="L87" s="2" t="s">
+      <c r="M87" s="2" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="88" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
         <v>1</v>
       </c>
@@ -5435,17 +5714,20 @@
       <c r="I88" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J88" s="3" t="s">
+      <c r="J88" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K88" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="K88" s="2" t="s">
+      <c r="L88" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="L88" s="2" t="s">
+      <c r="M88" s="2" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="89" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
         <v>1</v>
       </c>
@@ -5473,17 +5755,20 @@
       <c r="I89" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J89" s="3" t="s">
+      <c r="J89" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K89" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="K89" s="2" t="s">
+      <c r="L89" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="L89" s="2" t="s">
+      <c r="M89" s="2" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="90" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
         <v>1</v>
       </c>
@@ -5511,17 +5796,20 @@
       <c r="I90" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J90" s="3" t="s">
+      <c r="J90" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K90" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="K90" s="2" t="s">
+      <c r="L90" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="L90" s="2" t="s">
+      <c r="M90" s="2" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="91" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
         <v>1</v>
       </c>
@@ -5549,17 +5837,20 @@
       <c r="I91" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J91" s="3" t="s">
+      <c r="J91" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K91" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K91" s="2" t="s">
+      <c r="L91" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="L91" s="2" t="s">
+      <c r="M91" s="2" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="92" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
         <v>1</v>
       </c>
@@ -5587,17 +5878,20 @@
       <c r="I92" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J92" s="3" t="s">
+      <c r="J92" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K92" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K92" s="2" t="s">
+      <c r="L92" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="L92" s="2" t="s">
+      <c r="M92" s="2" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="93" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
         <v>1</v>
       </c>
@@ -5625,17 +5919,20 @@
       <c r="I93" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J93" s="3" t="s">
+      <c r="J93" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K93" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="K93" s="2" t="s">
+      <c r="L93" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="L93" s="2" t="s">
+      <c r="M93" s="2" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="94" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
         <v>1</v>
       </c>
@@ -5663,17 +5960,20 @@
       <c r="I94" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J94" s="3" t="s">
+      <c r="J94" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K94" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K94" s="2" t="s">
+      <c r="L94" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="L94" s="2" t="s">
+      <c r="M94" s="2" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="95" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
         <v>1</v>
       </c>
@@ -5701,17 +6001,20 @@
       <c r="I95" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J95" s="3" t="s">
+      <c r="J95" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K95" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K95" s="2" t="s">
+      <c r="L95" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="L95" s="2" t="s">
+      <c r="M95" s="2" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="96" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
         <v>1</v>
       </c>
@@ -5739,17 +6042,20 @@
       <c r="I96" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="J96" s="3" t="s">
+      <c r="J96" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K96" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="K96" s="2" t="s">
+      <c r="L96" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="L96" s="2" t="s">
+      <c r="M96" s="2" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="97" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
         <v>1</v>
       </c>
@@ -5777,17 +6083,20 @@
       <c r="I97" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="J97" s="3" t="s">
+      <c r="J97" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K97" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="K97" s="2" t="s">
+      <c r="L97" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="L97" s="2" t="s">
+      <c r="M97" s="2" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="98" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
         <v>1</v>
       </c>
@@ -5815,17 +6124,20 @@
       <c r="I98" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="J98" s="3" t="s">
+      <c r="J98" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K98" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="K98" s="2" t="s">
+      <c r="L98" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="L98" s="2" t="s">
+      <c r="M98" s="2" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="99" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
         <v>1</v>
       </c>
@@ -5853,17 +6165,20 @@
       <c r="I99" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="J99" s="3" t="s">
+      <c r="J99" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K99" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="K99" s="2" t="s">
+      <c r="L99" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="L99" s="2" t="s">
+      <c r="M99" s="2" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="100" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
         <v>1</v>
       </c>
@@ -5891,17 +6206,20 @@
       <c r="I100" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="J100" s="3" t="s">
+      <c r="J100" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K100" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="K100" s="2" t="s">
+      <c r="L100" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="L100" s="2" t="s">
+      <c r="M100" s="2" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="101" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
         <v>1</v>
       </c>
@@ -5929,17 +6247,20 @@
       <c r="I101" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="J101" s="3" t="s">
+      <c r="J101" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K101" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="K101" s="2" t="s">
+      <c r="L101" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="L101" s="2" t="s">
+      <c r="M101" s="2" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="102" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
         <v>1</v>
       </c>
@@ -5967,17 +6288,20 @@
       <c r="I102" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="J102" s="3" t="s">
+      <c r="J102" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K102" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="K102" s="2" t="s">
+      <c r="L102" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="L102" s="2" t="s">
+      <c r="M102" s="2" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="103" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="2" t="s">
         <v>1</v>
       </c>
@@ -6005,17 +6329,20 @@
       <c r="I103" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="J103" s="3" t="s">
+      <c r="J103" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K103" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="K103" s="2" t="s">
+      <c r="L103" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="L103" s="2" t="s">
+      <c r="M103" s="2" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="104" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="2" t="s">
         <v>1</v>
       </c>
@@ -6043,17 +6370,20 @@
       <c r="I104" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J104" s="3" t="s">
+      <c r="J104" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K104" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K104" s="2" t="s">
+      <c r="L104" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="L104" s="2" t="s">
+      <c r="M104" s="2" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="105" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="2" t="s">
         <v>1</v>
       </c>
@@ -6081,17 +6411,20 @@
       <c r="I105" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J105" s="3" t="s">
+      <c r="J105" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K105" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K105" s="2" t="s">
+      <c r="L105" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="L105" s="2" t="s">
+      <c r="M105" s="2" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="106" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="2" t="s">
         <v>1</v>
       </c>
@@ -6119,17 +6452,20 @@
       <c r="I106" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J106" s="3" t="s">
+      <c r="J106" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K106" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K106" s="2" t="s">
+      <c r="L106" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="L106" s="2" t="s">
+      <c r="M106" s="2" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="107" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="2" t="s">
         <v>1</v>
       </c>
@@ -6157,17 +6493,20 @@
       <c r="I107" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J107" s="3" t="s">
+      <c r="J107" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K107" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K107" s="2" t="s">
+      <c r="L107" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="L107" s="2" t="s">
+      <c r="M107" s="2" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="108" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="2" t="s">
         <v>1</v>
       </c>
@@ -6195,17 +6534,20 @@
       <c r="I108" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="J108" s="3" t="s">
+      <c r="J108" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K108" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K108" s="2" t="s">
+      <c r="L108" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="L108" s="2" t="s">
+      <c r="M108" s="2" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="109" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="2" t="s">
         <v>1</v>
       </c>
@@ -6233,17 +6575,20 @@
       <c r="I109" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="J109" s="3" t="s">
+      <c r="J109" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K109" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K109" s="2" t="s">
+      <c r="L109" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="L109" s="2" t="s">
+      <c r="M109" s="2" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="110" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="2" t="s">
         <v>1</v>
       </c>
@@ -6271,17 +6616,20 @@
       <c r="I110" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="J110" s="3" t="s">
+      <c r="J110" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K110" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K110" s="2" t="s">
+      <c r="L110" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="L110" s="2" t="s">
+      <c r="M110" s="2" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="111" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="2" t="s">
         <v>1</v>
       </c>
@@ -6309,17 +6657,20 @@
       <c r="I111" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J111" s="3" t="s">
+      <c r="J111" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K111" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="K111" s="2" t="s">
+      <c r="L111" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="L111" s="2" t="s">
+      <c r="M111" s="2" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="112" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="2" t="s">
         <v>1</v>
       </c>
@@ -6347,17 +6698,20 @@
       <c r="I112" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J112" s="3" t="s">
+      <c r="J112" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K112" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="K112" s="2" t="s">
+      <c r="L112" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="L112" s="2" t="s">
+      <c r="M112" s="2" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="113" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="2" t="s">
         <v>1</v>
       </c>
@@ -6385,17 +6739,20 @@
       <c r="I113" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J113" s="3" t="s">
+      <c r="J113" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K113" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="K113" s="2" t="s">
+      <c r="L113" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="L113" s="2" t="s">
+      <c r="M113" s="2" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="114" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="2" t="s">
         <v>1</v>
       </c>
@@ -6423,17 +6780,20 @@
       <c r="I114" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="J114" s="3" t="s">
+      <c r="J114" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="K114" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="K114" s="2" t="s">
+      <c r="L114" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="L114" s="2" t="s">
+      <c r="M114" s="2" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="115" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="2" t="s">
         <v>1</v>
       </c>
@@ -6461,17 +6821,20 @@
       <c r="I115" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="J115" s="3" t="s">
+      <c r="J115" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K115" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="K115" s="2" t="s">
+      <c r="L115" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="L115" s="2" t="s">
+      <c r="M115" s="2" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="116" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="2" t="s">
         <v>1</v>
       </c>
@@ -6499,17 +6862,20 @@
       <c r="I116" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="J116" s="3" t="s">
+      <c r="J116" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K116" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K116" s="2" t="s">
+      <c r="L116" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="L116" s="2" t="s">
+      <c r="M116" s="2" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="117" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="2" t="s">
         <v>1</v>
       </c>
@@ -6537,17 +6903,20 @@
       <c r="I117" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="J117" s="3" t="s">
+      <c r="J117" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K117" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K117" s="2" t="s">
+      <c r="L117" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="L117" s="2" t="s">
+      <c r="M117" s="2" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="118" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="2" t="s">
         <v>1</v>
       </c>
@@ -6575,17 +6944,20 @@
       <c r="I118" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="J118" s="3" t="s">
+      <c r="J118" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K118" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K118" s="2" t="s">
+      <c r="L118" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="L118" s="2" t="s">
+      <c r="M118" s="2" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="119" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="2" t="s">
         <v>1</v>
       </c>
@@ -6613,17 +6985,20 @@
       <c r="I119" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J119" s="3" t="s">
+      <c r="J119" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K119" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K119" s="2" t="s">
+      <c r="L119" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="L119" s="2" t="s">
+      <c r="M119" s="2" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="120" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="2" t="s">
         <v>1</v>
       </c>
@@ -6651,17 +7026,20 @@
       <c r="I120" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J120" s="3" t="s">
+      <c r="J120" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K120" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K120" s="2" t="s">
+      <c r="L120" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="L120" s="2" t="s">
+      <c r="M120" s="2" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="121" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="2" t="s">
         <v>1</v>
       </c>
@@ -6689,17 +7067,20 @@
       <c r="I121" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J121" s="3" t="s">
+      <c r="J121" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K121" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K121" s="2" t="s">
+      <c r="L121" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="L121" s="2" t="s">
+      <c r="M121" s="2" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="122" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="2" t="s">
         <v>1</v>
       </c>
@@ -6727,17 +7108,20 @@
       <c r="I122" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J122" s="3" t="s">
+      <c r="J122" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K122" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K122" s="2" t="s">
+      <c r="L122" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="L122" s="2" t="s">
+      <c r="M122" s="2" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="123" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="2" t="s">
         <v>1</v>
       </c>
@@ -6765,17 +7149,20 @@
       <c r="I123" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="J123" s="3" t="s">
+      <c r="J123" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="K123" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K123" s="2" t="s">
+      <c r="L123" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="L123" s="2" t="s">
+      <c r="M123" s="2" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="124" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="2" t="s">
         <v>1</v>
       </c>
@@ -6803,17 +7190,20 @@
       <c r="I124" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="J124" s="3" t="s">
+      <c r="J124" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="K124" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K124" s="2" t="s">
+      <c r="L124" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="L124" s="2" t="s">
+      <c r="M124" s="2" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="125" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="2" t="s">
         <v>1</v>
       </c>
@@ -6841,17 +7231,20 @@
       <c r="I125" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="J125" s="3" t="s">
+      <c r="J125" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="K125" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K125" s="2" t="s">
+      <c r="L125" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="L125" s="2" t="s">
+      <c r="M125" s="2" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="126" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="2" t="s">
         <v>1</v>
       </c>
@@ -6879,17 +7272,20 @@
       <c r="I126" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="J126" s="3" t="s">
+      <c r="J126" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="K126" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K126" s="2" t="s">
+      <c r="L126" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="L126" s="2" t="s">
+      <c r="M126" s="2" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="127" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="2" t="s">
         <v>1</v>
       </c>
@@ -6917,17 +7313,20 @@
       <c r="I127" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="J127" s="3" t="s">
+      <c r="J127" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="K127" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K127" s="2" t="s">
+      <c r="L127" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="L127" s="2" t="s">
+      <c r="M127" s="2" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="128" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="2" t="s">
         <v>1</v>
       </c>
@@ -6955,17 +7354,20 @@
       <c r="I128" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="J128" s="3" t="s">
+      <c r="J128" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="K128" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K128" s="2" t="s">
+      <c r="L128" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="L128" s="2" t="s">
+      <c r="M128" s="2" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="129" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="2" t="s">
         <v>1</v>
       </c>
@@ -6993,17 +7395,20 @@
       <c r="I129" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="J129" s="3" t="s">
+      <c r="J129" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="K129" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K129" s="2" t="s">
+      <c r="L129" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="L129" s="2" t="s">
+      <c r="M129" s="2" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="130" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="2" t="s">
         <v>1</v>
       </c>
@@ -7031,17 +7436,20 @@
       <c r="I130" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="J130" s="3" t="s">
+      <c r="J130" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="K130" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="K130" s="2" t="s">
+      <c r="L130" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="L130" s="2" t="s">
+      <c r="M130" s="2" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="131" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="2" t="s">
         <v>1</v>
       </c>
@@ -7069,17 +7477,20 @@
       <c r="I131" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="J131" s="3" t="s">
+      <c r="J131" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="K131" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="K131" s="2" t="s">
+      <c r="L131" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="L131" s="2" t="s">
+      <c r="M131" s="2" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="132" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="2" t="s">
         <v>1</v>
       </c>
@@ -7107,17 +7518,20 @@
       <c r="I132" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J132" s="3" t="s">
+      <c r="J132" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K132" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K132" s="2" t="s">
+      <c r="L132" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="L132" s="2" t="s">
+      <c r="M132" s="2" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="133" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="2" t="s">
         <v>1</v>
       </c>
@@ -7145,17 +7559,20 @@
       <c r="I133" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J133" s="3" t="s">
+      <c r="J133" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K133" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K133" s="2" t="s">
+      <c r="L133" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="L133" s="2" t="s">
+      <c r="M133" s="2" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="134" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="2" t="s">
         <v>1</v>
       </c>
@@ -7183,17 +7600,20 @@
       <c r="I134" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J134" s="3" t="s">
+      <c r="J134" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K134" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K134" s="2" t="s">
+      <c r="L134" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="L134" s="2" t="s">
+      <c r="M134" s="2" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="135" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="2" t="s">
         <v>1</v>
       </c>
@@ -7221,17 +7641,20 @@
       <c r="I135" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="J135" s="3" t="s">
+      <c r="J135" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="K135" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K135" s="2" t="s">
+      <c r="L135" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="L135" s="2" t="s">
+      <c r="M135" s="2" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="136" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="2" t="s">
         <v>1</v>
       </c>
@@ -7259,17 +7682,20 @@
       <c r="I136" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="J136" s="3" t="s">
+      <c r="J136" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="K136" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K136" s="2" t="s">
+      <c r="L136" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="L136" s="2" t="s">
+      <c r="M136" s="2" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="137" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="2" t="s">
         <v>1</v>
       </c>
@@ -7297,17 +7723,20 @@
       <c r="I137" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="J137" s="3" t="s">
+      <c r="J137" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="K137" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K137" s="2" t="s">
+      <c r="L137" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="L137" s="2" t="s">
+      <c r="M137" s="2" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="138" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="2" t="s">
         <v>1</v>
       </c>
@@ -7335,17 +7764,20 @@
       <c r="I138" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="J138" s="3" t="s">
+      <c r="J138" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="K138" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K138" s="2" t="s">
+      <c r="L138" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="L138" s="2" t="s">
+      <c r="M138" s="2" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="139" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="2" t="s">
         <v>1</v>
       </c>
@@ -7373,17 +7805,20 @@
       <c r="I139" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="J139" s="3" t="s">
+      <c r="J139" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="K139" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K139" s="2" t="s">
+      <c r="L139" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="L139" s="2" t="s">
+      <c r="M139" s="2" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="140" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="2" t="s">
         <v>1</v>
       </c>
@@ -7411,17 +7846,20 @@
       <c r="I140" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="J140" s="3" t="s">
+      <c r="J140" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="K140" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K140" s="2" t="s">
+      <c r="L140" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="L140" s="2" t="s">
+      <c r="M140" s="2" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="141" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="2" t="s">
         <v>1</v>
       </c>
@@ -7449,17 +7887,20 @@
       <c r="I141" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="J141" s="3" t="s">
+      <c r="J141" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="K141" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K141" s="2" t="s">
+      <c r="L141" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="L141" s="2" t="s">
+      <c r="M141" s="2" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="142" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="2" t="s">
         <v>1</v>
       </c>
@@ -7487,17 +7928,20 @@
       <c r="I142" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="J142" s="3" t="s">
+      <c r="J142" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="K142" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K142" s="2" t="s">
+      <c r="L142" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="L142" s="2" t="s">
+      <c r="M142" s="2" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="143" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="2" t="s">
         <v>2</v>
       </c>
@@ -7525,17 +7969,20 @@
       <c r="I143" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="J143" s="3" t="s">
+      <c r="J143" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K143" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="K143" s="2" t="s">
+      <c r="L143" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="L143" s="2" t="s">
+      <c r="M143" s="2" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="144" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="2" t="s">
         <v>2</v>
       </c>
@@ -7563,17 +8010,20 @@
       <c r="I144" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="J144" s="3" t="s">
+      <c r="J144" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K144" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="K144" s="2" t="s">
+      <c r="L144" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="L144" s="2" t="s">
+      <c r="M144" s="2" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="145" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="2" t="s">
         <v>2</v>
       </c>
@@ -7601,17 +8051,20 @@
       <c r="I145" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="J145" s="3" t="s">
+      <c r="J145" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K145" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="K145" s="2" t="s">
+      <c r="L145" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="L145" s="2" t="s">
+      <c r="M145" s="2" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="146" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="2" t="s">
         <v>1</v>
       </c>
@@ -7639,17 +8092,20 @@
       <c r="I146" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J146" s="3" t="s">
+      <c r="J146" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K146" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K146" s="2" t="s">
+      <c r="L146" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="L146" s="2" t="s">
+      <c r="M146" s="2" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="147" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="2" t="s">
         <v>1</v>
       </c>
@@ -7677,17 +8133,20 @@
       <c r="I147" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J147" s="3" t="s">
+      <c r="J147" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K147" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K147" s="2" t="s">
+      <c r="L147" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="L147" s="2" t="s">
+      <c r="M147" s="2" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="148" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="2" t="s">
         <v>1</v>
       </c>
@@ -7715,17 +8174,20 @@
       <c r="I148" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J148" s="3" t="s">
+      <c r="J148" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K148" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K148" s="2" t="s">
+      <c r="L148" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="L148" s="2" t="s">
+      <c r="M148" s="2" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="149" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="2" t="s">
         <v>1</v>
       </c>
@@ -7753,17 +8215,20 @@
       <c r="I149" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J149" s="3" t="s">
+      <c r="J149" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K149" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K149" s="2" t="s">
+      <c r="L149" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="L149" s="2" t="s">
+      <c r="M149" s="2" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="150" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="2" t="s">
         <v>1</v>
       </c>
@@ -7791,17 +8256,20 @@
       <c r="I150" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="J150" s="3" t="s">
+      <c r="J150" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="K150" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K150" s="2" t="s">
+      <c r="L150" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="L150" s="2" t="s">
+      <c r="M150" s="2" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="151" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="2" t="s">
         <v>1</v>
       </c>
@@ -7829,17 +8297,20 @@
       <c r="I151" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J151" s="3" t="s">
+      <c r="J151" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K151" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K151" s="2" t="s">
+      <c r="L151" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="L151" s="2" t="s">
+      <c r="M151" s="2" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="152" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="2" t="s">
         <v>1</v>
       </c>
@@ -7867,17 +8338,20 @@
       <c r="I152" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="J152" s="3" t="s">
+      <c r="J152" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K152" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K152" s="2" t="s">
+      <c r="L152" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="L152" s="2" t="s">
+      <c r="M152" s="2" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="153" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="2" t="s">
         <v>1</v>
       </c>
@@ -7905,17 +8379,20 @@
       <c r="I153" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="J153" s="3" t="s">
+      <c r="J153" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K153" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K153" s="2" t="s">
+      <c r="L153" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="L153" s="2" t="s">
+      <c r="M153" s="2" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="154" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="2" t="s">
         <v>1</v>
       </c>
@@ -7943,17 +8420,20 @@
       <c r="I154" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="J154" s="3" t="s">
+      <c r="J154" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K154" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K154" s="2" t="s">
+      <c r="L154" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="L154" s="2" t="s">
+      <c r="M154" s="2" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="155" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="2" t="s">
         <v>1</v>
       </c>
@@ -7981,17 +8461,20 @@
       <c r="I155" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="J155" s="3" t="s">
+      <c r="J155" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K155" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K155" s="2" t="s">
+      <c r="L155" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="L155" s="2" t="s">
+      <c r="M155" s="2" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="156" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="2" t="s">
         <v>1</v>
       </c>
@@ -8019,17 +8502,20 @@
       <c r="I156" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="J156" s="3" t="s">
+      <c r="J156" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K156" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K156" s="2" t="s">
+      <c r="L156" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="L156" s="2" t="s">
+      <c r="M156" s="2" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="157" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="2" t="s">
         <v>1</v>
       </c>
@@ -8057,17 +8543,20 @@
       <c r="I157" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="J157" s="3" t="s">
+      <c r="J157" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K157" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K157" s="2" t="s">
+      <c r="L157" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="L157" s="2" t="s">
+      <c r="M157" s="2" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="158" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="2" t="s">
         <v>1</v>
       </c>
@@ -8095,17 +8584,20 @@
       <c r="I158" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J158" s="3" t="s">
+      <c r="J158" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K158" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K158" s="2" t="s">
+      <c r="L158" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="L158" s="2" t="s">
+      <c r="M158" s="2" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="159" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="2" t="s">
         <v>1</v>
       </c>
@@ -8133,17 +8625,20 @@
       <c r="I159" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J159" s="3" t="s">
+      <c r="J159" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K159" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K159" s="2" t="s">
+      <c r="L159" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="L159" s="2" t="s">
+      <c r="M159" s="2" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="160" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="2" t="s">
         <v>1</v>
       </c>
@@ -8171,17 +8666,20 @@
       <c r="I160" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J160" s="3" t="s">
+      <c r="J160" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K160" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K160" s="2" t="s">
+      <c r="L160" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="L160" s="2" t="s">
+      <c r="M160" s="2" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="161" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="2" t="s">
         <v>1</v>
       </c>
@@ -8209,17 +8707,20 @@
       <c r="I161" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="J161" s="3" t="s">
+      <c r="J161" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K161" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="K161" s="2" t="s">
+      <c r="L161" s="2" t="s">
         <v>468</v>
       </c>
-      <c r="L161" s="2" t="s">
+      <c r="M161" s="2" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="162" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="2" t="s">
         <v>1</v>
       </c>
@@ -8247,17 +8748,20 @@
       <c r="I162" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="J162" s="3" t="s">
+      <c r="J162" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K162" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="K162" s="2" t="s">
+      <c r="L162" s="2" t="s">
         <v>468</v>
       </c>
-      <c r="L162" s="2" t="s">
+      <c r="M162" s="2" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="163" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="2" t="s">
         <v>1</v>
       </c>
@@ -8285,17 +8789,20 @@
       <c r="I163" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="J163" s="3" t="s">
+      <c r="J163" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K163" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="K163" s="2" t="s">
+      <c r="L163" s="2" t="s">
         <v>468</v>
       </c>
-      <c r="L163" s="2" t="s">
+      <c r="M163" s="2" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="164" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="2" t="s">
         <v>1</v>
       </c>
@@ -8323,17 +8830,20 @@
       <c r="I164" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="J164" s="3" t="s">
+      <c r="J164" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="K164" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="K164" s="2" t="s">
+      <c r="L164" s="2" t="s">
         <v>468</v>
       </c>
-      <c r="L164" s="2" t="s">
+      <c r="M164" s="2" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="165" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="2" t="s">
         <v>1</v>
       </c>
@@ -8361,17 +8871,20 @@
       <c r="I165" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="J165" s="3" t="s">
+      <c r="J165" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K165" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="K165" s="2" t="s">
+      <c r="L165" s="2" t="s">
         <v>468</v>
       </c>
-      <c r="L165" s="2" t="s">
+      <c r="M165" s="2" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="166" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="2" t="s">
         <v>1</v>
       </c>
@@ -8399,17 +8912,20 @@
       <c r="I166" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="J166" s="3" t="s">
+      <c r="J166" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="K166" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K166" s="2" t="s">
+      <c r="L166" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="L166" s="2" t="s">
+      <c r="M166" s="2" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="167" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="2" t="s">
         <v>1</v>
       </c>
@@ -8437,17 +8953,20 @@
       <c r="I167" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="J167" s="3" t="s">
+      <c r="J167" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="K167" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K167" s="2" t="s">
+      <c r="L167" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="L167" s="2" t="s">
+      <c r="M167" s="2" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="168" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="2" t="s">
         <v>1</v>
       </c>
@@ -8475,17 +8994,20 @@
       <c r="I168" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="J168" s="3" t="s">
+      <c r="J168" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="K168" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K168" s="2" t="s">
+      <c r="L168" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="L168" s="2" t="s">
+      <c r="M168" s="2" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="169" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="2" t="s">
         <v>1</v>
       </c>
@@ -8513,17 +9035,20 @@
       <c r="I169" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="J169" s="3" t="s">
+      <c r="J169" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="K169" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K169" s="2" t="s">
+      <c r="L169" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L169" s="2" t="s">
+      <c r="M169" s="2" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="170" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="2" t="s">
         <v>1</v>
       </c>
@@ -8551,17 +9076,20 @@
       <c r="I170" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="J170" s="3" t="s">
+      <c r="J170" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="K170" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K170" s="2" t="s">
+      <c r="L170" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L170" s="2" t="s">
+      <c r="M170" s="2" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="171" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="2" t="s">
         <v>1</v>
       </c>
@@ -8589,17 +9117,20 @@
       <c r="I171" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="J171" s="3" t="s">
+      <c r="J171" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K171" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="K171" s="2" t="s">
+      <c r="L171" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="L171" s="2" t="s">
+      <c r="M171" s="2" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="172" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="2" t="s">
         <v>1</v>
       </c>
@@ -8627,17 +9158,20 @@
       <c r="I172" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="J172" s="3" t="s">
+      <c r="J172" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K172" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="K172" s="2" t="s">
+      <c r="L172" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="L172" s="2" t="s">
+      <c r="M172" s="2" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="173" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="2" t="s">
         <v>1</v>
       </c>
@@ -8665,17 +9199,20 @@
       <c r="I173" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="J173" s="3" t="s">
+      <c r="J173" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K173" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K173" s="2" t="s">
+      <c r="L173" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="L173" s="2" t="s">
+      <c r="M173" s="2" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="174" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="2" t="s">
         <v>1</v>
       </c>
@@ -8703,17 +9240,20 @@
       <c r="I174" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="J174" s="3" t="s">
+      <c r="J174" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K174" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K174" s="2" t="s">
+      <c r="L174" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="L174" s="2" t="s">
+      <c r="M174" s="2" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="175" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="2" t="s">
         <v>1</v>
       </c>
@@ -8741,17 +9281,20 @@
       <c r="I175" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="J175" s="3" t="s">
+      <c r="J175" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K175" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K175" s="2" t="s">
+      <c r="L175" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L175" s="2" t="s">
+      <c r="M175" s="2" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="176" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="2" t="s">
         <v>1</v>
       </c>
@@ -8779,17 +9322,20 @@
       <c r="I176" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="J176" s="3" t="s">
+      <c r="J176" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K176" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K176" s="2" t="s">
+      <c r="L176" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L176" s="2" t="s">
+      <c r="M176" s="2" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="177" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="2" t="s">
         <v>1</v>
       </c>
@@ -8817,17 +9363,20 @@
       <c r="I177" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="J177" s="3" t="s">
+      <c r="J177" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K177" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K177" s="2" t="s">
+      <c r="L177" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L177" s="2" t="s">
+      <c r="M177" s="2" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="178" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="2" t="s">
         <v>1</v>
       </c>
@@ -8855,17 +9404,20 @@
       <c r="I178" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="J178" s="3" t="s">
+      <c r="J178" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K178" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K178" s="2" t="s">
+      <c r="L178" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L178" s="2" t="s">
+      <c r="M178" s="2" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="179" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="2" t="s">
         <v>1</v>
       </c>
@@ -8893,17 +9445,20 @@
       <c r="I179" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="J179" s="3" t="s">
+      <c r="J179" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K179" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="K179" s="2" t="s">
+      <c r="L179" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="L179" s="2" t="s">
+      <c r="M179" s="2" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="180" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="2" t="s">
         <v>1</v>
       </c>
@@ -8931,17 +9486,20 @@
       <c r="I180" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="J180" s="3" t="s">
+      <c r="J180" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K180" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="K180" s="2" t="s">
+      <c r="L180" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="L180" s="2" t="s">
+      <c r="M180" s="2" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="181" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="2" t="s">
         <v>1</v>
       </c>
@@ -8969,17 +9527,20 @@
       <c r="I181" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="J181" s="3" t="s">
+      <c r="J181" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K181" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="K181" s="2" t="s">
+      <c r="L181" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="L181" s="2" t="s">
+      <c r="M181" s="2" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="182" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="2" t="s">
         <v>1</v>
       </c>
@@ -9007,17 +9568,20 @@
       <c r="I182" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="J182" s="3" t="s">
+      <c r="J182" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K182" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K182" s="2" t="s">
+      <c r="L182" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L182" s="2" t="s">
+      <c r="M182" s="2" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="183" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="2" t="s">
         <v>1</v>
       </c>
@@ -9045,17 +9609,20 @@
       <c r="I183" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="J183" s="3" t="s">
+      <c r="J183" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K183" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K183" s="2" t="s">
+      <c r="L183" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L183" s="2" t="s">
+      <c r="M183" s="2" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="184" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="2" t="s">
         <v>1</v>
       </c>
@@ -9083,17 +9650,20 @@
       <c r="I184" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="J184" s="3" t="s">
+      <c r="J184" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K184" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K184" s="2" t="s">
+      <c r="L184" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L184" s="2" t="s">
+      <c r="M184" s="2" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="185" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="2" t="s">
         <v>1</v>
       </c>
@@ -9121,17 +9691,20 @@
       <c r="I185" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="J185" s="3" t="s">
+      <c r="J185" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K185" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K185" s="2" t="s">
+      <c r="L185" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L185" s="2" t="s">
+      <c r="M185" s="2" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="186" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="2" t="s">
         <v>1</v>
       </c>
@@ -9159,17 +9732,20 @@
       <c r="I186" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J186" s="3" t="s">
+      <c r="J186" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K186" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K186" s="2" t="s">
+      <c r="L186" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L186" s="2" t="s">
+      <c r="M186" s="2" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="187" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="2" t="s">
         <v>1</v>
       </c>
@@ -9197,17 +9773,20 @@
       <c r="I187" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J187" s="3" t="s">
+      <c r="J187" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K187" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K187" s="2" t="s">
+      <c r="L187" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L187" s="2" t="s">
+      <c r="M187" s="2" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="188" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="2" t="s">
         <v>1</v>
       </c>
@@ -9235,17 +9814,20 @@
       <c r="I188" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J188" s="3" t="s">
+      <c r="J188" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K188" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K188" s="2" t="s">
+      <c r="L188" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L188" s="2" t="s">
+      <c r="M188" s="2" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="189" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="2" t="s">
         <v>1</v>
       </c>
@@ -9273,17 +9855,20 @@
       <c r="I189" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J189" s="3" t="s">
+      <c r="J189" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K189" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K189" s="2" t="s">
+      <c r="L189" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L189" s="2" t="s">
+      <c r="M189" s="2" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="190" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="2" t="s">
         <v>1</v>
       </c>
@@ -9311,17 +9896,20 @@
       <c r="I190" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J190" s="3" t="s">
+      <c r="J190" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K190" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K190" s="2" t="s">
+      <c r="L190" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L190" s="2" t="s">
+      <c r="M190" s="2" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="191" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="2" t="s">
         <v>1</v>
       </c>
@@ -9349,17 +9937,20 @@
       <c r="I191" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J191" s="3" t="s">
+      <c r="J191" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K191" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K191" s="2" t="s">
+      <c r="L191" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L191" s="2" t="s">
+      <c r="M191" s="2" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="192" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="2" t="s">
         <v>1</v>
       </c>
@@ -9387,17 +9978,20 @@
       <c r="I192" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J192" s="3" t="s">
+      <c r="J192" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K192" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K192" s="2" t="s">
+      <c r="L192" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L192" s="2" t="s">
+      <c r="M192" s="2" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="193" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="2" t="s">
         <v>1</v>
       </c>
@@ -9425,17 +10019,20 @@
       <c r="I193" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="J193" s="3" t="s">
+      <c r="J193" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K193" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K193" s="2" t="s">
+      <c r="L193" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L193" s="2" t="s">
+      <c r="M193" s="2" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="194" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="2" t="s">
         <v>1</v>
       </c>
@@ -9463,17 +10060,20 @@
       <c r="I194" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="J194" s="3" t="s">
+      <c r="J194" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K194" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K194" s="2" t="s">
+      <c r="L194" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L194" s="2" t="s">
+      <c r="M194" s="2" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="195" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="2" t="s">
         <v>1</v>
       </c>
@@ -9501,17 +10101,20 @@
       <c r="I195" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="J195" s="3" t="s">
+      <c r="J195" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K195" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K195" s="2" t="s">
+      <c r="L195" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L195" s="2" t="s">
+      <c r="M195" s="2" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="196" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="2" t="s">
         <v>1</v>
       </c>
@@ -9539,17 +10142,20 @@
       <c r="I196" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="J196" s="3" t="s">
+      <c r="J196" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K196" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K196" s="2" t="s">
+      <c r="L196" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L196" s="2" t="s">
+      <c r="M196" s="2" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="197" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="2" t="s">
         <v>1</v>
       </c>
@@ -9577,17 +10183,20 @@
       <c r="I197" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="J197" s="3" t="s">
+      <c r="J197" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K197" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K197" s="2" t="s">
+      <c r="L197" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L197" s="2" t="s">
+      <c r="M197" s="2" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="198" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="2" t="s">
         <v>1</v>
       </c>
@@ -9615,17 +10224,20 @@
       <c r="I198" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="J198" s="3" t="s">
+      <c r="J198" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="K198" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K198" s="2" t="s">
+      <c r="L198" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L198" s="2" t="s">
+      <c r="M198" s="2" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="199" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="2" t="s">
         <v>1</v>
       </c>
@@ -9653,17 +10265,20 @@
       <c r="I199" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="J199" s="3" t="s">
+      <c r="J199" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="K199" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K199" s="2" t="s">
+      <c r="L199" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L199" s="2" t="s">
+      <c r="M199" s="2" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="200" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="2" t="s">
         <v>1</v>
       </c>
@@ -9691,17 +10306,20 @@
       <c r="I200" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="J200" s="3" t="s">
+      <c r="J200" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="K200" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K200" s="2" t="s">
+      <c r="L200" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L200" s="2" t="s">
+      <c r="M200" s="2" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="201" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="2" t="s">
         <v>1</v>
       </c>
@@ -9729,17 +10347,20 @@
       <c r="I201" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="J201" s="3" t="s">
+      <c r="J201" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="K201" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K201" s="2" t="s">
+      <c r="L201" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L201" s="2" t="s">
+      <c r="M201" s="2" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="202" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="2" t="s">
         <v>1</v>
       </c>
@@ -9767,17 +10388,20 @@
       <c r="I202" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="J202" s="3" t="s">
+      <c r="J202" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="K202" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K202" s="2" t="s">
+      <c r="L202" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L202" s="2" t="s">
+      <c r="M202" s="2" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="203" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="2" t="s">
         <v>1</v>
       </c>
@@ -9805,17 +10429,20 @@
       <c r="I203" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="J203" s="3" t="s">
+      <c r="J203" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="K203" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K203" s="2" t="s">
+      <c r="L203" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L203" s="2" t="s">
+      <c r="M203" s="2" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="204" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="2" t="s">
         <v>1</v>
       </c>
@@ -9843,17 +10470,20 @@
       <c r="I204" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="J204" s="3" t="s">
+      <c r="J204" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="K204" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K204" s="2" t="s">
+      <c r="L204" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L204" s="2" t="s">
+      <c r="M204" s="2" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="205" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="2" t="s">
         <v>1</v>
       </c>
@@ -9881,17 +10511,20 @@
       <c r="I205" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="J205" s="3" t="s">
+      <c r="J205" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="K205" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K205" s="2" t="s">
+      <c r="L205" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L205" s="2" t="s">
+      <c r="M205" s="2" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="206" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="2" t="s">
         <v>1</v>
       </c>
@@ -9919,17 +10552,20 @@
       <c r="I206" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J206" s="3" t="s">
+      <c r="J206" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K206" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K206" s="2" t="s">
+      <c r="L206" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L206" s="2" t="s">
+      <c r="M206" s="2" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="207" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="2" t="s">
         <v>1</v>
       </c>
@@ -9957,17 +10593,20 @@
       <c r="I207" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J207" s="3" t="s">
+      <c r="J207" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K207" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K207" s="2" t="s">
+      <c r="L207" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L207" s="2" t="s">
+      <c r="M207" s="2" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="208" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="2" t="s">
         <v>1</v>
       </c>
@@ -9995,17 +10634,20 @@
       <c r="I208" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J208" s="3" t="s">
+      <c r="J208" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K208" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K208" s="2" t="s">
+      <c r="L208" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L208" s="2" t="s">
+      <c r="M208" s="2" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="209" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="2" t="s">
         <v>1</v>
       </c>
@@ -10033,17 +10675,20 @@
       <c r="I209" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J209" s="3" t="s">
+      <c r="J209" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K209" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K209" s="2" t="s">
+      <c r="L209" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L209" s="2" t="s">
+      <c r="M209" s="2" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="210" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="2" t="s">
         <v>1</v>
       </c>
@@ -10071,17 +10716,20 @@
       <c r="I210" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J210" s="3" t="s">
+      <c r="J210" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K210" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="K210" s="2" t="s">
+      <c r="L210" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="L210" s="2" t="s">
+      <c r="M210" s="2" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="211" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="2" t="s">
         <v>1</v>
       </c>
@@ -10109,17 +10757,20 @@
       <c r="I211" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J211" s="3" t="s">
+      <c r="J211" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K211" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="K211" s="2" t="s">
+      <c r="L211" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="L211" s="2" t="s">
+      <c r="M211" s="2" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="212" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="2" t="s">
         <v>1</v>
       </c>
@@ -10147,17 +10798,20 @@
       <c r="I212" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J212" s="3" t="s">
+      <c r="J212" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K212" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="K212" s="2" t="s">
+      <c r="L212" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="L212" s="2" t="s">
+      <c r="M212" s="2" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="213" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="2" t="s">
         <v>1</v>
       </c>
@@ -10185,17 +10839,20 @@
       <c r="I213" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="J213" s="3" t="s">
+      <c r="J213" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K213" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K213" s="2" t="s">
+      <c r="L213" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="L213" s="2" t="s">
+      <c r="M213" s="2" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="214" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="2" t="s">
         <v>1</v>
       </c>
@@ -10223,17 +10880,20 @@
       <c r="I214" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="J214" s="3" t="s">
+      <c r="J214" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K214" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K214" s="2" t="s">
+      <c r="L214" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="L214" s="2" t="s">
+      <c r="M214" s="2" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="215" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="2" t="s">
         <v>1</v>
       </c>
@@ -10261,17 +10921,20 @@
       <c r="I215" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="J215" s="3" t="s">
+      <c r="J215" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K215" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K215" s="2" t="s">
+      <c r="L215" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="L215" s="2" t="s">
+      <c r="M215" s="2" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="216" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="2" t="s">
         <v>1</v>
       </c>
@@ -10299,17 +10962,20 @@
       <c r="I216" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="J216" s="3" t="s">
+      <c r="J216" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K216" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="K216" s="2" t="s">
+      <c r="L216" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="L216" s="2" t="s">
+      <c r="M216" s="2" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="217" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="2" t="s">
         <v>1</v>
       </c>
@@ -10337,17 +11003,20 @@
       <c r="I217" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J217" s="3" t="s">
+      <c r="J217" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K217" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="K217" s="2" t="s">
+      <c r="L217" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="L217" s="2" t="s">
+      <c r="M217" s="2" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="218" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="2" t="s">
         <v>1</v>
       </c>
@@ -10375,17 +11044,20 @@
       <c r="I218" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="J218" s="3" t="s">
+      <c r="J218" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K218" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="K218" s="2" t="s">
+      <c r="L218" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="L218" s="2" t="s">
+      <c r="M218" s="2" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="219" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="2" t="s">
         <v>1</v>
       </c>
@@ -10413,17 +11085,20 @@
       <c r="I219" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="J219" s="3" t="s">
+      <c r="J219" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K219" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="K219" s="2" t="s">
+      <c r="L219" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="L219" s="2" t="s">
+      <c r="M219" s="2" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="220" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="2" t="s">
         <v>1</v>
       </c>
@@ -10451,17 +11126,20 @@
       <c r="I220" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J220" s="3" t="s">
+      <c r="J220" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K220" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="K220" s="2" t="s">
+      <c r="L220" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="L220" s="2" t="s">
+      <c r="M220" s="2" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="221" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="2" t="s">
         <v>1</v>
       </c>
@@ -10489,17 +11167,20 @@
       <c r="I221" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J221" s="3" t="s">
+      <c r="J221" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K221" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="K221" s="2" t="s">
+      <c r="L221" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="L221" s="2" t="s">
+      <c r="M221" s="2" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="222" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="2" t="s">
         <v>1</v>
       </c>
@@ -10527,17 +11208,20 @@
       <c r="I222" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J222" s="3" t="s">
+      <c r="J222" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K222" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="K222" s="2" t="s">
+      <c r="L222" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="L222" s="2" t="s">
+      <c r="M222" s="2" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="223" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="2" t="s">
         <v>1</v>
       </c>
@@ -10565,17 +11249,20 @@
       <c r="I223" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="J223" s="3" t="s">
+      <c r="J223" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="K223" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="K223" s="2" t="s">
+      <c r="L223" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="L223" s="2" t="s">
+      <c r="M223" s="2" t="s">
         <v>532</v>
       </c>
     </row>
-    <row r="224" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="2" t="s">
         <v>1</v>
       </c>
@@ -10603,17 +11290,20 @@
       <c r="I224" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="J224" s="3" t="s">
+      <c r="J224" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="K224" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="K224" s="2" t="s">
+      <c r="L224" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="L224" s="2" t="s">
+      <c r="M224" s="2" t="s">
         <v>532</v>
       </c>
     </row>
-    <row r="225" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="2" t="s">
         <v>1</v>
       </c>
@@ -10641,17 +11331,20 @@
       <c r="I225" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J225" s="3" t="s">
+      <c r="J225" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K225" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K225" s="2" t="s">
+      <c r="L225" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L225" s="2" t="s">
+      <c r="M225" s="2" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="226" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="2" t="s">
         <v>1</v>
       </c>
@@ -10679,17 +11372,20 @@
       <c r="I226" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J226" s="3" t="s">
+      <c r="J226" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K226" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K226" s="2" t="s">
+      <c r="L226" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L226" s="2" t="s">
+      <c r="M226" s="2" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="227" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="2" t="s">
         <v>1</v>
       </c>
@@ -10717,17 +11413,20 @@
       <c r="I227" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J227" s="3" t="s">
+      <c r="J227" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K227" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K227" s="2" t="s">
+      <c r="L227" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L227" s="2" t="s">
+      <c r="M227" s="2" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="228" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="2" t="s">
         <v>1</v>
       </c>
@@ -10755,17 +11454,20 @@
       <c r="I228" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J228" s="3" t="s">
+      <c r="J228" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K228" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K228" s="2" t="s">
+      <c r="L228" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L228" s="2" t="s">
+      <c r="M228" s="2" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="229" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="2" t="s">
         <v>1</v>
       </c>
@@ -10793,17 +11495,20 @@
       <c r="I229" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J229" s="3" t="s">
+      <c r="J229" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K229" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K229" s="2" t="s">
+      <c r="L229" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L229" s="2" t="s">
+      <c r="M229" s="2" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="230" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="2" t="s">
         <v>1</v>
       </c>
@@ -10831,17 +11536,20 @@
       <c r="I230" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J230" s="3" t="s">
+      <c r="J230" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K230" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K230" s="2" t="s">
+      <c r="L230" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L230" s="2" t="s">
+      <c r="M230" s="2" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="231" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="2" t="s">
         <v>1</v>
       </c>
@@ -10869,17 +11577,20 @@
       <c r="I231" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J231" s="3" t="s">
+      <c r="J231" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K231" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K231" s="2" t="s">
+      <c r="L231" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L231" s="2" t="s">
+      <c r="M231" s="2" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="232" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="2" t="s">
         <v>1</v>
       </c>
@@ -10907,17 +11618,20 @@
       <c r="I232" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J232" s="3" t="s">
+      <c r="J232" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K232" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="K232" s="2" t="s">
+      <c r="L232" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="L232" s="2" t="s">
+      <c r="M232" s="2" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="233" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="2" t="s">
         <v>1</v>
       </c>
@@ -10945,17 +11659,20 @@
       <c r="I233" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J233" s="3" t="s">
+      <c r="J233" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K233" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="K233" s="2" t="s">
+      <c r="L233" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="L233" s="2" t="s">
+      <c r="M233" s="2" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="234" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="2" t="s">
         <v>1</v>
       </c>
@@ -10983,17 +11700,20 @@
       <c r="I234" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J234" s="3" t="s">
+      <c r="J234" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K234" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K234" s="2" t="s">
+      <c r="L234" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L234" s="2" t="s">
+      <c r="M234" s="2" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="235" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="2" t="s">
         <v>1</v>
       </c>
@@ -11021,17 +11741,20 @@
       <c r="I235" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J235" s="3" t="s">
+      <c r="J235" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K235" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K235" s="2" t="s">
+      <c r="L235" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L235" s="2" t="s">
+      <c r="M235" s="2" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="236" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="2" t="s">
         <v>1</v>
       </c>
@@ -11059,17 +11782,20 @@
       <c r="I236" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J236" s="3" t="s">
+      <c r="J236" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K236" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K236" s="2" t="s">
+      <c r="L236" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L236" s="2" t="s">
+      <c r="M236" s="2" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="237" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="2" t="s">
         <v>1</v>
       </c>
@@ -11097,17 +11823,20 @@
       <c r="I237" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J237" s="3" t="s">
+      <c r="J237" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K237" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K237" s="2" t="s">
+      <c r="L237" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L237" s="2" t="s">
+      <c r="M237" s="2" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="238" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="2" t="s">
         <v>1</v>
       </c>
@@ -11135,17 +11864,20 @@
       <c r="I238" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="J238" s="3" t="s">
+      <c r="J238" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K238" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K238" s="2" t="s">
+      <c r="L238" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L238" s="2" t="s">
+      <c r="M238" s="2" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="239" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="2" t="s">
         <v>2</v>
       </c>
@@ -11173,17 +11905,20 @@
       <c r="I239" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J239" s="3" t="s">
+      <c r="J239" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K239" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="K239" s="2" t="s">
+      <c r="L239" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="L239" s="2" t="s">
+      <c r="M239" s="2" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="240" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="2" t="s">
         <v>2</v>
       </c>
@@ -11211,17 +11946,20 @@
       <c r="I240" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J240" s="3" t="s">
+      <c r="J240" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K240" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="K240" s="2" t="s">
+      <c r="L240" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="L240" s="2" t="s">
+      <c r="M240" s="2" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="241" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="2" t="s">
         <v>2</v>
       </c>
@@ -11249,17 +11987,20 @@
       <c r="I241" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J241" s="3" t="s">
+      <c r="J241" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K241" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="K241" s="2" t="s">
+      <c r="L241" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="L241" s="2" t="s">
+      <c r="M241" s="2" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="242" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="2" t="s">
         <v>2</v>
       </c>
@@ -11287,17 +12028,20 @@
       <c r="I242" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J242" s="3" t="s">
+      <c r="J242" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K242" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="K242" s="2" t="s">
+      <c r="L242" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="L242" s="2" t="s">
+      <c r="M242" s="2" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="243" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="2" t="s">
         <v>2</v>
       </c>
@@ -11325,17 +12069,20 @@
       <c r="I243" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J243" s="3" t="s">
+      <c r="J243" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K243" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="K243" s="2" t="s">
+      <c r="L243" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="L243" s="2" t="s">
+      <c r="M243" s="2" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="244" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="2" t="s">
         <v>1</v>
       </c>
@@ -11363,17 +12110,20 @@
       <c r="I244" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J244" s="3" t="s">
+      <c r="J244" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K244" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="K244" s="2" t="s">
+      <c r="L244" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="L244" s="2" t="s">
+      <c r="M244" s="2" t="s">
         <v>532</v>
       </c>
     </row>
-    <row r="245" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="2" t="s">
         <v>1</v>
       </c>
@@ -11401,17 +12151,20 @@
       <c r="I245" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J245" s="3" t="s">
+      <c r="J245" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K245" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="K245" s="2" t="s">
+      <c r="L245" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="L245" s="2" t="s">
+      <c r="M245" s="2" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="246" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="2" t="s">
         <v>1</v>
       </c>
@@ -11439,17 +12192,20 @@
       <c r="I246" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J246" s="3" t="s">
+      <c r="J246" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K246" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K246" s="2" t="s">
+      <c r="L246" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="L246" s="2" t="s">
+      <c r="M246" s="2" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="247" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="2" t="s">
         <v>1</v>
       </c>
@@ -11477,17 +12233,20 @@
       <c r="I247" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J247" s="3" t="s">
+      <c r="J247" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K247" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K247" s="2" t="s">
+      <c r="L247" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="L247" s="2" t="s">
+      <c r="M247" s="2" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="248" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="2" t="s">
         <v>1</v>
       </c>
@@ -11515,17 +12274,20 @@
       <c r="I248" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="J248" s="3" t="s">
+      <c r="J248" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="K248" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K248" s="2" t="s">
+      <c r="L248" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L248" s="2" t="s">
+      <c r="M248" s="2" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="249" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="2" t="s">
         <v>1</v>
       </c>
@@ -11553,17 +12315,20 @@
       <c r="I249" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="J249" s="3" t="s">
+      <c r="J249" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="K249" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K249" s="2" t="s">
+      <c r="L249" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L249" s="2" t="s">
+      <c r="M249" s="2" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="250" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="2" t="s">
         <v>1</v>
       </c>
@@ -11591,17 +12356,20 @@
       <c r="I250" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="J250" s="3" t="s">
+      <c r="J250" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="K250" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K250" s="2" t="s">
+      <c r="L250" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L250" s="2" t="s">
+      <c r="M250" s="2" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="251" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="2" t="s">
         <v>1</v>
       </c>
@@ -11629,17 +12397,20 @@
       <c r="I251" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="J251" s="3" t="s">
+      <c r="J251" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="K251" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K251" s="2" t="s">
+      <c r="L251" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L251" s="2" t="s">
+      <c r="M251" s="2" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="252" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="2" t="s">
         <v>1</v>
       </c>
@@ -11667,17 +12438,20 @@
       <c r="I252" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="J252" s="3" t="s">
+      <c r="J252" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K252" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K252" s="2" t="s">
+      <c r="L252" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L252" s="2" t="s">
+      <c r="M252" s="2" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="253" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="2" t="s">
         <v>1</v>
       </c>
@@ -11705,17 +12479,20 @@
       <c r="I253" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="J253" s="3" t="s">
+      <c r="J253" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="K253" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K253" s="2" t="s">
+      <c r="L253" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L253" s="2" t="s">
+      <c r="M253" s="2" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="254" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="2" t="s">
         <v>1</v>
       </c>
@@ -11743,17 +12520,20 @@
       <c r="I254" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="J254" s="3" t="s">
+      <c r="J254" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="K254" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K254" s="2" t="s">
+      <c r="L254" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L254" s="2" t="s">
+      <c r="M254" s="2" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="255" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="2" t="s">
         <v>1</v>
       </c>
@@ -11781,17 +12561,20 @@
       <c r="I255" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="J255" s="3" t="s">
+      <c r="J255" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="K255" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K255" s="2" t="s">
+      <c r="L255" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L255" s="2" t="s">
+      <c r="M255" s="2" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="256" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="2" t="s">
         <v>1</v>
       </c>
@@ -11819,17 +12602,20 @@
       <c r="I256" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="J256" s="3" t="s">
+      <c r="J256" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="K256" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K256" s="2" t="s">
+      <c r="L256" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L256" s="2" t="s">
+      <c r="M256" s="2" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="257" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="2" t="s">
         <v>1</v>
       </c>
@@ -11857,17 +12643,20 @@
       <c r="I257" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="J257" s="3" t="s">
+      <c r="J257" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="K257" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K257" s="2" t="s">
+      <c r="L257" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L257" s="2" t="s">
+      <c r="M257" s="2" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="258" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="2" t="s">
         <v>1</v>
       </c>
@@ -11895,17 +12684,20 @@
       <c r="I258" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="J258" s="3" t="s">
+      <c r="J258" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="K258" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K258" s="2" t="s">
+      <c r="L258" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L258" s="2" t="s">
+      <c r="M258" s="2" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="259" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="2" t="s">
         <v>1</v>
       </c>
@@ -11933,17 +12725,20 @@
       <c r="I259" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="J259" s="3" t="s">
+      <c r="J259" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="K259" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K259" s="2" t="s">
+      <c r="L259" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L259" s="2" t="s">
+      <c r="M259" s="2" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="260" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="2" t="s">
         <v>1</v>
       </c>
@@ -11971,17 +12766,20 @@
       <c r="I260" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="J260" s="3" t="s">
+      <c r="J260" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="K260" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K260" s="2" t="s">
+      <c r="L260" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L260" s="2" t="s">
+      <c r="M260" s="2" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="261" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A261" s="2" t="s">
         <v>1</v>
       </c>
@@ -12009,17 +12807,20 @@
       <c r="I261" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="J261" s="3" t="s">
+      <c r="J261" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="K261" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K261" s="2" t="s">
+      <c r="L261" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L261" s="2" t="s">
+      <c r="M261" s="2" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="262" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262" s="2" t="s">
         <v>1</v>
       </c>
@@ -12047,17 +12848,20 @@
       <c r="I262" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J262" s="3" t="s">
+      <c r="J262" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="K262" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K262" s="2" t="s">
+      <c r="L262" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L262" s="2" t="s">
+      <c r="M262" s="2" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="263" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263" s="2" t="s">
         <v>1</v>
       </c>
@@ -12085,17 +12889,20 @@
       <c r="I263" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="J263" s="3" t="s">
+      <c r="J263" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K263" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K263" s="2" t="s">
+      <c r="L263" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L263" s="2" t="s">
+      <c r="M263" s="2" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="264" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264" s="2" t="s">
         <v>1</v>
       </c>
@@ -12123,17 +12930,20 @@
       <c r="I264" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="J264" s="3" t="s">
+      <c r="J264" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K264" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K264" s="2" t="s">
+      <c r="L264" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L264" s="2" t="s">
+      <c r="M264" s="2" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="265" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="2" t="s">
         <v>1</v>
       </c>
@@ -12161,17 +12971,20 @@
       <c r="I265" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="J265" s="3" t="s">
+      <c r="J265" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K265" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K265" s="2" t="s">
+      <c r="L265" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L265" s="2" t="s">
+      <c r="M265" s="2" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="266" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="2" t="s">
         <v>1</v>
       </c>
@@ -12199,17 +13012,20 @@
       <c r="I266" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="J266" s="3" t="s">
+      <c r="J266" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K266" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K266" s="2" t="s">
+      <c r="L266" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L266" s="2" t="s">
+      <c r="M266" s="2" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="267" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="2" t="s">
         <v>1</v>
       </c>
@@ -12237,17 +13053,20 @@
       <c r="I267" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="J267" s="3" t="s">
+      <c r="J267" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="K267" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="K267" s="2" t="s">
+      <c r="L267" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="L267" s="2" t="s">
+      <c r="M267" s="2" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="268" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268" s="2" t="s">
         <v>1</v>
       </c>
@@ -12275,17 +13094,20 @@
       <c r="I268" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J268" s="3" t="s">
+      <c r="J268" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K268" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="K268" s="2" t="s">
+      <c r="L268" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="L268" s="2" t="s">
+      <c r="M268" s="2" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="269" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="2" t="s">
         <v>1</v>
       </c>
@@ -12313,17 +13135,20 @@
       <c r="I269" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="J269" s="3" t="s">
+      <c r="J269" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="K269" s="3" t="s">
         <v>454</v>
       </c>
-      <c r="K269" s="2" t="s">
+      <c r="L269" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="L269" s="2" t="s">
+      <c r="M269" s="2" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="270" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270" s="2" t="s">
         <v>3</v>
       </c>
@@ -12351,17 +13176,20 @@
       <c r="I270" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="J270" s="3" t="s">
+      <c r="J270" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="K270" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="K270" s="2" t="s">
+      <c r="L270" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="L270" s="2" t="s">
+      <c r="M270" s="2" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="271" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271" s="2" t="s">
         <v>3</v>
       </c>
@@ -12389,17 +13217,20 @@
       <c r="I271" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="J271" s="3" t="s">
+      <c r="J271" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="K271" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="K271" s="2" t="s">
+      <c r="L271" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="L271" s="2" t="s">
+      <c r="M271" s="2" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="272" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A272" s="2" t="s">
         <v>1</v>
       </c>
@@ -12427,17 +13258,20 @@
       <c r="I272" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="J272" s="3" t="s">
+      <c r="J272" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K272" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="K272" s="2" t="s">
+      <c r="L272" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="L272" s="2" t="s">
+      <c r="M272" s="2" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="273" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="2" t="s">
         <v>1</v>
       </c>
@@ -12465,17 +13299,20 @@
       <c r="I273" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="J273" s="3" t="s">
+      <c r="J273" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="K273" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="K273" s="2" t="s">
+      <c r="L273" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="L273" s="2" t="s">
+      <c r="M273" s="2" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="274" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="2" t="s">
         <v>1</v>
       </c>
@@ -12503,17 +13340,20 @@
       <c r="I274" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="J274" s="3" t="s">
+      <c r="J274" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="K274" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="K274" s="2" t="s">
+      <c r="L274" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="L274" s="2" t="s">
+      <c r="M274" s="2" t="s">
         <v>538</v>
       </c>
     </row>
-    <row r="275" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="2" t="s">
         <v>1</v>
       </c>
@@ -12541,17 +13381,20 @@
       <c r="I275" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="J275" s="3" t="s">
+      <c r="J275" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="K275" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="K275" s="2" t="s">
+      <c r="L275" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="L275" s="2" t="s">
+      <c r="M275" s="2" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="276" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="2" t="s">
         <v>4</v>
       </c>
@@ -12579,17 +13422,20 @@
       <c r="I276" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="J276" s="3" t="s">
+      <c r="J276" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="K276" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="K276" s="2" t="s">
+      <c r="L276" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="L276" s="2" t="s">
+      <c r="M276" s="2" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="277" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="2" t="s">
         <v>5</v>
       </c>
@@ -12617,13 +13463,16 @@
       <c r="I277" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="J277" s="3" t="s">
+      <c r="J277" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="K277" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="K277" s="2" t="s">
+      <c r="L277" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="L277" s="2" t="s">
+      <c r="M277" s="2" t="s">
         <v>539</v>
       </c>
     </row>
